--- a/sitepreview/trust/v1.7.3/CodeSystem-Participants.xlsx
+++ b/sitepreview/trust/v1.7.3/CodeSystem-Participants.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T09:02:00+00:00</t>
+    <t>2026-10-02T10:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
